--- a/data/raincoast_sites.xlsx
+++ b/data/raincoast_sites.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ubcca-my.sharepoint.com/personal/smichauc_student_ubc_ca/Documents/Anchor Raincoast/Raincoast_foragefish/kmz_raincoast_sites/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/soleilmichaud/Desktop/Raincoast_shinyapp/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="279" documentId="11_0C92DFD08F79A8D366075C52F37BD2720AC0C882" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A7A8C15-F1CC-C24B-AF93-51E441FC454A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C494B145-87D8-1847-B7C8-D41C7B56593E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13480" yWindow="9760" windowWidth="15260" windowHeight="8940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14520" yWindow="620" windowWidth="14280" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="438">
   <si>
     <t>layer</t>
   </si>
@@ -746,13 +747,601 @@
   </si>
   <si>
     <t>Description</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>lo</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>Alex Fraser</t>
+  </si>
+  <si>
+    <t>Marsh</t>
+  </si>
+  <si>
+    <t>ALK</t>
+  </si>
+  <si>
+    <t>Alaksen channel</t>
+  </si>
+  <si>
+    <t>Richmond Cambie</t>
+  </si>
+  <si>
+    <t>Deerin Island</t>
+  </si>
+  <si>
+    <t>DIR</t>
+  </si>
+  <si>
+    <t>Deering Island Ref</t>
+  </si>
+  <si>
+    <t>Deering Island Reference</t>
+  </si>
+  <si>
+    <t>DJG</t>
+  </si>
+  <si>
+    <t>Jetty Gap</t>
+  </si>
+  <si>
+    <t>Woodward Dam</t>
+  </si>
+  <si>
+    <t>DUF1</t>
+  </si>
+  <si>
+    <t>Frenchies Channel 1</t>
+  </si>
+  <si>
+    <t>DUF2</t>
+  </si>
+  <si>
+    <t>Frenchies Channel 2</t>
+  </si>
+  <si>
+    <t>DUFO</t>
+  </si>
+  <si>
+    <t>Frenchies Beach</t>
+  </si>
+  <si>
+    <t>Frenchies Outside</t>
+  </si>
+  <si>
+    <t>DUG1</t>
+  </si>
+  <si>
+    <t>Gunn Impact</t>
+  </si>
+  <si>
+    <t>DUG1DF1</t>
+  </si>
+  <si>
+    <t>Gunn Impact Additional Channel</t>
+  </si>
+  <si>
+    <t>DUG2</t>
+  </si>
+  <si>
+    <t>Gunn Reference</t>
+  </si>
+  <si>
+    <t>DUG2DF1</t>
+  </si>
+  <si>
+    <t>Gunn Reference Additional Channel</t>
+  </si>
+  <si>
+    <t>DUJG</t>
+  </si>
+  <si>
+    <t>Kirkland Jetty Gap</t>
+  </si>
+  <si>
+    <t>DUK1</t>
+  </si>
+  <si>
+    <t>Kirkland Channel North</t>
+  </si>
+  <si>
+    <t>Kirkland Channel 1</t>
+  </si>
+  <si>
+    <t>DUK2</t>
+  </si>
+  <si>
+    <t>Kirkland Channel 2</t>
+  </si>
+  <si>
+    <t>DUWD</t>
+  </si>
+  <si>
+    <t>Mid Roberts Bank Old</t>
+  </si>
+  <si>
+    <t>Sandflat</t>
+  </si>
+  <si>
+    <t>Mid Roberts Bank New</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Intercauseway North</t>
+  </si>
+  <si>
+    <t>Intercauseway South</t>
+  </si>
+  <si>
+    <t>E5</t>
+  </si>
+  <si>
+    <t>South Ferry</t>
+  </si>
+  <si>
+    <t>Tug Basin</t>
+  </si>
+  <si>
+    <t>Beach</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>Fyke net site 1</t>
+  </si>
+  <si>
+    <t>Woodward Marsh Fyke 1</t>
+  </si>
+  <si>
+    <t>Woodward Marsh Fyke 2</t>
+  </si>
+  <si>
+    <t>F2</t>
+  </si>
+  <si>
+    <t>Fyke net site 2</t>
+  </si>
+  <si>
+    <t>Woodward Marsh Fyke 3</t>
+  </si>
+  <si>
+    <t>F2DF1</t>
+  </si>
+  <si>
+    <t>F2DF2</t>
+  </si>
+  <si>
+    <t>Woodward Island Channel Fyke</t>
+  </si>
+  <si>
+    <t>F3</t>
+  </si>
+  <si>
+    <t>Fyke net site 3</t>
+  </si>
+  <si>
+    <t>FRP</t>
+  </si>
+  <si>
+    <t>Fraser River Park</t>
+  </si>
+  <si>
+    <t>Gilbert Beach</t>
+  </si>
+  <si>
+    <t>GDF1</t>
+  </si>
+  <si>
+    <t>Garry Point Channel fyke</t>
+  </si>
+  <si>
+    <t>Grauer Channel Fyke</t>
+  </si>
+  <si>
+    <t>Grauer Lands Fyke 1</t>
+  </si>
+  <si>
+    <t>Grauer Lands Fyke 2</t>
+  </si>
+  <si>
+    <t>This is from the dataset, the other one is from the KMZ</t>
+  </si>
+  <si>
+    <t>Steveston Jetty Fyke 10</t>
+  </si>
+  <si>
+    <t>Steveston Jetty Fyke 11</t>
+  </si>
+  <si>
+    <t>Steveston Jetty Fyke 12</t>
+  </si>
+  <si>
+    <t>Steveston Jetty Fyke 3</t>
+  </si>
+  <si>
+    <t>Steveston Jetty Fyke 4</t>
+  </si>
+  <si>
+    <t>Steveston Jetty Fyke 5</t>
+  </si>
+  <si>
+    <t>Steveston Jetty Fyke 6</t>
+  </si>
+  <si>
+    <t>Steveston Jetty Fyke 7</t>
+  </si>
+  <si>
+    <t>Steveston Jetty Fyke 8</t>
+  </si>
+  <si>
+    <t>Steveston Jetty Fyke 9</t>
+  </si>
+  <si>
+    <t>Steveston Jetty fyke 1</t>
+  </si>
+  <si>
+    <t>Steveston South Jetty Fyke 1</t>
+  </si>
+  <si>
+    <t>Westham Island Fyke 1</t>
+  </si>
+  <si>
+    <t>Westham Island Fyke 2</t>
+  </si>
+  <si>
+    <t>Steveston South Jetty Fyke 2</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>River</t>
+  </si>
+  <si>
+    <t>JF</t>
+  </si>
+  <si>
+    <t>Jet Fuel</t>
+  </si>
+  <si>
+    <t>Garry Point</t>
+  </si>
+  <si>
+    <t>Steveston</t>
+  </si>
+  <si>
+    <t>Steveston Jetty Channel</t>
+  </si>
+  <si>
+    <t>Steveston Jetty ChannelMarsh</t>
+  </si>
+  <si>
+    <t>Steveston Jetty Gap</t>
+  </si>
+  <si>
+    <t>Steveston channel</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>BCIT</t>
+  </si>
+  <si>
+    <t>North Richmond</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>North Arm East</t>
+  </si>
+  <si>
+    <t>Westham West</t>
+  </si>
+  <si>
+    <t>M14DF1</t>
+  </si>
+  <si>
+    <t>Westham West Channel Fyke</t>
+  </si>
+  <si>
+    <t>Westham West Channel fyke</t>
+  </si>
+  <si>
+    <t>North Arm Middle</t>
+  </si>
+  <si>
+    <t>Swishwash Island Beach</t>
+  </si>
+  <si>
+    <t>North Arm West North</t>
+  </si>
+  <si>
+    <t>North Arm West South</t>
+  </si>
+  <si>
+    <t>M1DF1</t>
+  </si>
+  <si>
+    <t>Garry Point Channel Fyke 1</t>
+  </si>
+  <si>
+    <t>M1DF2</t>
+  </si>
+  <si>
+    <t>Garry Point Channel Fyke 2</t>
+  </si>
+  <si>
+    <t>Westham</t>
+  </si>
+  <si>
+    <t>Westham North</t>
+  </si>
+  <si>
+    <t>Westham Island</t>
+  </si>
+  <si>
+    <t>Westham Island South Channel</t>
+  </si>
+  <si>
+    <t>Brunswick Point</t>
+  </si>
+  <si>
+    <t>South Arm marshes</t>
+  </si>
+  <si>
+    <t>Woodward Island</t>
+  </si>
+  <si>
+    <t>Woodward Island Channel</t>
+  </si>
+  <si>
+    <t>Woodward Island Marsh</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>McDonald Slough Back</t>
+  </si>
+  <si>
+    <t>M7DF1</t>
+  </si>
+  <si>
+    <t>McDonald Restoration Channel</t>
+  </si>
+  <si>
+    <t>M9DF1</t>
+  </si>
+  <si>
+    <t>McDonald Beach Channel Fyke</t>
+  </si>
+  <si>
+    <t>Mission</t>
+  </si>
+  <si>
+    <t>Pirate's Cove Beach</t>
+  </si>
+  <si>
+    <t>Pirate's Cove Marsh</t>
+  </si>
+  <si>
+    <t>Point Roberts</t>
+  </si>
+  <si>
+    <t>Shaughnessy Street Park</t>
+  </si>
+  <si>
+    <t>Tilbury East</t>
+  </si>
+  <si>
+    <t>Tilbury East Bay</t>
+  </si>
+  <si>
+    <t>Tilbury Island (downstream)</t>
+  </si>
+  <si>
+    <t>Tilbury Island Downstream</t>
+  </si>
+  <si>
+    <t>Tilbury Island upstream</t>
+  </si>
+  <si>
+    <t>Tree Island Slough</t>
+  </si>
+  <si>
+    <t>Tugboat</t>
+  </si>
+  <si>
+    <t>Upper Deas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Westham West </t>
+  </si>
+  <si>
+    <t>North Arm Jetty Breach</t>
+  </si>
+  <si>
+    <t>North Arm Breach Upstream</t>
+  </si>
+  <si>
+    <t>North Arm Jetty Breach Upstream</t>
+  </si>
+  <si>
+    <t>NRB</t>
+  </si>
+  <si>
+    <t>Blackbuoy Channel</t>
+  </si>
+  <si>
+    <t>Mid Roberts Bank</t>
+  </si>
+  <si>
+    <t>NSP</t>
+  </si>
+  <si>
+    <t>North Scotch Pond</t>
+  </si>
+  <si>
+    <t>OWB</t>
+  </si>
+  <si>
+    <t>Old Woodward Dam Breach</t>
+  </si>
+  <si>
+    <t>QSC</t>
+  </si>
+  <si>
+    <t>Quayside Comp</t>
+  </si>
+  <si>
+    <t>Quayside Compensation</t>
+  </si>
+  <si>
+    <t>RM</t>
+  </si>
+  <si>
+    <t>SAM 2</t>
+  </si>
+  <si>
+    <t>South Arm Marsh 1</t>
+  </si>
+  <si>
+    <t>Gunn Island/ South Arm Marsh 2</t>
+  </si>
+  <si>
+    <t>South Arm Marshes Site 2</t>
+  </si>
+  <si>
+    <t>Iona North</t>
+  </si>
+  <si>
+    <t>Iona South</t>
+  </si>
+  <si>
+    <t>Richmond North</t>
+  </si>
+  <si>
+    <t>Steveston North</t>
+  </si>
+  <si>
+    <t>Richmond South</t>
+  </si>
+  <si>
+    <t>Steveston South</t>
+  </si>
+  <si>
+    <t>North Roberts Bank</t>
+  </si>
+  <si>
+    <t>SF6</t>
+  </si>
+  <si>
+    <t>South Roberts Bank</t>
+  </si>
+  <si>
+    <t>North Arm Jetty</t>
+  </si>
+  <si>
+    <t>Steveston East Breach/ Steveston Jetty East Breach</t>
+  </si>
+  <si>
+    <t>SLC</t>
+  </si>
+  <si>
+    <t>Sapperton Landing Comp</t>
+  </si>
+  <si>
+    <t>Sapperton Landing Compensation</t>
+  </si>
+  <si>
+    <t>South Scotch Pond</t>
+  </si>
+  <si>
+    <t>Swishwash</t>
+  </si>
+  <si>
+    <t>TLR</t>
+  </si>
+  <si>
+    <t>Tugboat Landing Ref</t>
+  </si>
+  <si>
+    <t>Tugboat Landing Reference</t>
+  </si>
+  <si>
+    <t>WB</t>
+  </si>
+  <si>
+    <t>Woods Foot Bridge</t>
+  </si>
+  <si>
+    <t>Swishwash South</t>
+  </si>
+  <si>
+    <t>TIS</t>
+  </si>
+  <si>
+    <t>TIU</t>
+  </si>
+  <si>
+    <t>TID</t>
+  </si>
+  <si>
+    <t>Marh</t>
+  </si>
+  <si>
+    <t>Roberts Bank</t>
+  </si>
+  <si>
+    <t>Intercauseway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intercauseway </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grauer Lands </t>
+  </si>
+  <si>
+    <t>North Arm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swishwash Island </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garry Point </t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Arm Marshes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Arm </t>
+  </si>
+  <si>
+    <t>McDonald Restoration Channel ( Slough Channel Fyke)</t>
+  </si>
+  <si>
+    <t>McDonald Restoration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">McDonald Slough </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -768,8 +1357,23 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -788,6 +1392,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -801,14 +1429,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -824,10 +1471,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1227,233 +1870,233 @@
         <v>49.158883333333328</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>69</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="E6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6">
         <v>-122.97345</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6">
         <v>49.160316666666667</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="4">
+      <c r="E7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="3">
         <v>-122.9820669600538</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="3">
         <v>49.185026738921437</v>
       </c>
     </row>
-    <row r="8" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="4">
+      <c r="E8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="3">
         <v>-122.98374678308561</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>49.182991288554327</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="4">
+      <c r="E9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="3">
         <v>-122.9855617663673</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="3">
         <v>49.18369931220245</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="4">
+      <c r="E10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="3">
         <v>-122.97957532066791</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="3">
         <v>49.181441895277651</v>
       </c>
     </row>
-    <row r="11" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="4">
+      <c r="E11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="3">
         <v>-122.97995845731531</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="3">
         <v>49.181130908109658</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="4">
+      <c r="E12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="3">
         <v>-122.9796898557065</v>
       </c>
-      <c r="G12" s="4">
+      <c r="G12" s="3">
         <v>49.182444697984813</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="4">
+      <c r="E13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="3">
         <v>-122.98042598388309</v>
       </c>
-      <c r="G13" s="4">
+      <c r="G13" s="3">
         <v>49.182832179299631</v>
       </c>
     </row>
-    <row r="14" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="4">
+      <c r="E14" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="3">
         <v>-122.9801378538284</v>
       </c>
-      <c r="G14" s="4">
+      <c r="G14" s="3">
         <v>49.182007005653688</v>
       </c>
     </row>
-    <row r="15" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="4">
+      <c r="E15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="3">
         <v>-122.9808944138797</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G15" s="3">
         <v>49.182666682781388</v>
       </c>
     </row>
@@ -3699,4 +4342,4778 @@
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9936F9E5-DE66-474B-A721-3C8D41A7E572}">
+  <dimension ref="A1:H246"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" style="4"/>
+    <col min="2" max="2" width="28.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="4"/>
+    <col min="4" max="4" width="22.6640625" style="4" customWidth="1"/>
+    <col min="5" max="16384" width="10.83203125" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E2" s="4">
+        <v>49.161423999999997</v>
+      </c>
+      <c r="F2" s="4">
+        <v>-122.94448</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E3" s="3">
+        <v>49.109200000000001</v>
+      </c>
+      <c r="F3" s="3">
+        <v>-123.17834999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="4">
+        <v>49.158883333333328</v>
+      </c>
+      <c r="F4" s="4">
+        <v>-122.93955</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="4">
+        <v>49.160316666666667</v>
+      </c>
+      <c r="F5" s="4">
+        <v>-122.97345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="4">
+        <v>49.185026738921437</v>
+      </c>
+      <c r="F6" s="4">
+        <v>-122.9820669600538</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="4">
+        <v>49.182991288554327</v>
+      </c>
+      <c r="F7" s="4">
+        <v>-122.98374678308561</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="4">
+        <v>49.18369931220245</v>
+      </c>
+      <c r="F8" s="4">
+        <v>-122.9855617663673</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" s="4">
+        <v>49.181441895277651</v>
+      </c>
+      <c r="F9" s="4">
+        <v>-122.97957532066791</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="4">
+        <v>49.181130908109658</v>
+      </c>
+      <c r="F10" s="4">
+        <v>-122.97995845731531</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="4">
+        <v>49.182444697984813</v>
+      </c>
+      <c r="F11" s="4">
+        <v>-122.9796898557065</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" s="4">
+        <v>49.182832179299631</v>
+      </c>
+      <c r="F12" s="4">
+        <v>-122.98042598388309</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E13" s="4">
+        <v>49.182007005653688</v>
+      </c>
+      <c r="F13" s="4">
+        <v>-122.9801378538284</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" s="4">
+        <v>49.182666682781388</v>
+      </c>
+      <c r="F14" s="4">
+        <v>-122.9808944138797</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E15" s="4">
+        <v>49.218816666666669</v>
+      </c>
+      <c r="F15" s="4">
+        <v>-123.18656666666671</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E16" s="4">
+        <v>49.222192999999997</v>
+      </c>
+      <c r="F16" s="4">
+        <v>-123.211923</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E17" s="4">
+        <v>49.105393999999997</v>
+      </c>
+      <c r="F17" s="4">
+        <v>-123.122331</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="4">
+        <v>49.114139762455103</v>
+      </c>
+      <c r="F19" s="4">
+        <v>-123.0679601703763</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E20" s="4">
+        <v>49.115586135285639</v>
+      </c>
+      <c r="F20" s="4">
+        <v>-123.0691161397236</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="E21" s="4">
+        <v>49.126262333009009</v>
+      </c>
+      <c r="F21" s="4">
+        <v>-123.0535455448957</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E22" s="4">
+        <v>49.11849999999999</v>
+      </c>
+      <c r="F22" s="4">
+        <v>-123.0633333333333</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="E23" s="4">
+        <v>49.101502000000004</v>
+      </c>
+      <c r="F23" s="4">
+        <v>-123.11639599999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E24" s="4">
+        <v>49.102258999999997</v>
+      </c>
+      <c r="F24" s="4">
+        <v>-123.111491</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E25" s="7">
+        <v>49.102752000000002</v>
+      </c>
+      <c r="F25" s="7">
+        <v>-123.114031</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="E26" s="7">
+        <v>49.102752000000002</v>
+      </c>
+      <c r="F26" s="7">
+        <v>-123.114031</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="E27" s="4">
+        <v>49.104515999999997</v>
+      </c>
+      <c r="F27" s="4">
+        <v>-123.103812</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E28" s="4">
+        <v>49.104519000000003</v>
+      </c>
+      <c r="F28" s="4">
+        <v>-123.100228</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E29" s="4">
+        <v>49.098331000000002</v>
+      </c>
+      <c r="F29" s="4">
+        <v>-123.11362800000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E30" s="4">
+        <v>49.098624000000001</v>
+      </c>
+      <c r="F30" s="4">
+        <v>-123.113435</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="E31" s="4">
+        <v>49.111030999999997</v>
+      </c>
+      <c r="F31" s="4">
+        <v>-123.103117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E32" s="4">
+        <v>49.110686999999999</v>
+      </c>
+      <c r="F32" s="4">
+        <v>-123.103393</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="E33" s="4">
+        <v>49.106042000000002</v>
+      </c>
+      <c r="F33" s="4">
+        <v>-123.106375</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="E34" s="4">
+        <v>49.105393999999997</v>
+      </c>
+      <c r="F34" s="4">
+        <v>-123.122331</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="E35" s="4">
+        <v>49.033650000000009</v>
+      </c>
+      <c r="F35" s="4">
+        <v>-123.1819</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="E36" s="4">
+        <v>49.031330084425832</v>
+      </c>
+      <c r="F36" s="4">
+        <v>-123.1665375355785</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="E37" s="4">
+        <v>49.026766666666667</v>
+      </c>
+      <c r="F37" s="4">
+        <v>-123.1394833333333</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="E38" s="4">
+        <v>49.017476636555628</v>
+      </c>
+      <c r="F38" s="4">
+        <v>-123.1267014558412</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E40" s="7">
+        <v>49.026225497140267</v>
+      </c>
+      <c r="F40" s="7">
+        <v>-123.1487448802512</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E41" s="7">
+        <v>49.026366666666668</v>
+      </c>
+      <c r="F41" s="7">
+        <v>-123.15066666666669</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E42" s="7">
+        <v>49.026225497140267</v>
+      </c>
+      <c r="F42" s="7">
+        <v>-123.1487448802512</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E43" s="7">
+        <v>49.026366666666668</v>
+      </c>
+      <c r="F43" s="7">
+        <v>-123.15066666666669</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E44" s="7">
+        <v>49.026225497140267</v>
+      </c>
+      <c r="F44" s="7">
+        <v>-123.1487448802512</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="7">
+        <v>49.026366666666668</v>
+      </c>
+      <c r="F45" s="7">
+        <v>-123.15066666666669</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E46" s="4">
+        <v>49.128733333333336</v>
+      </c>
+      <c r="F46" s="4">
+        <v>-123.2084333333333</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E47" s="8">
+        <v>49.100282999999997</v>
+      </c>
+      <c r="F47" s="8">
+        <v>-123.1408</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E48" s="8">
+        <v>49.100282999999997</v>
+      </c>
+      <c r="F48" s="8">
+        <v>-123.1408</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E49" s="8">
+        <v>49.100700000000003</v>
+      </c>
+      <c r="F49" s="8">
+        <v>-123.149417</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="E50" s="8">
+        <v>49.100700000000003</v>
+      </c>
+      <c r="F50" s="8">
+        <v>-123.149417</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="E51" s="5">
+        <v>49.100700000000003</v>
+      </c>
+      <c r="F51" s="5">
+        <v>-123.149417</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="E52" s="5">
+        <v>49.100700000000003</v>
+      </c>
+      <c r="F52" s="5">
+        <v>-123.149417</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="E53" s="5">
+        <v>49.100700000000003</v>
+      </c>
+      <c r="F53" s="5">
+        <v>-123.149417</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E54" s="5">
+        <v>49.102583000000003</v>
+      </c>
+      <c r="F54" s="5">
+        <v>-123.14815</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E55" s="5">
+        <v>49.102583000000003</v>
+      </c>
+      <c r="F55" s="5">
+        <v>-123.14815</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E56" s="4">
+        <v>49.208750000000002</v>
+      </c>
+      <c r="F56" s="4">
+        <v>-123.15295</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E58" s="4">
+        <v>49.11172883489526</v>
+      </c>
+      <c r="F58" s="4">
+        <v>-123.14762227410139</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="E59" s="4">
+        <v>49.11506879886759</v>
+      </c>
+      <c r="F59" s="4">
+        <v>-123.1557221825894</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E60" s="4">
+        <v>49.112770944158051</v>
+      </c>
+      <c r="F60" s="4">
+        <v>-123.1503829991025</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="E61" s="7">
+        <v>49.127783000000001</v>
+      </c>
+      <c r="F61" s="7">
+        <v>-123.201683</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E62" s="7">
+        <v>49.169533000000001</v>
+      </c>
+      <c r="F62" s="7">
+        <v>-123.20249800000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E63" s="7">
+        <v>49.213283333333337</v>
+      </c>
+      <c r="F63" s="7">
+        <v>-123.20489999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E64" s="7">
+        <v>49.213283333333337</v>
+      </c>
+      <c r="F64" s="7">
+        <v>-123.20489999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E65" s="7">
+        <v>49.213283333333337</v>
+      </c>
+      <c r="F65" s="7">
+        <v>-123.20489999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E66" s="7">
+        <v>49.219799999999999</v>
+      </c>
+      <c r="F66" s="7">
+        <v>-123.21565</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E67" s="7">
+        <v>49.219799999999999</v>
+      </c>
+      <c r="F67" s="7">
+        <v>-123.21565</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E68" s="7">
+        <v>49.219799999999999</v>
+      </c>
+      <c r="F68" s="7">
+        <v>-123.21565</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E69" s="7">
+        <v>49.219799999999999</v>
+      </c>
+      <c r="F69" s="7">
+        <v>-123.21565</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E70" s="4">
+        <v>49.137673522825537</v>
+      </c>
+      <c r="F70" s="4">
+        <v>-123.2014084148939</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A71" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="E71" s="4">
+        <v>49.135963327367953</v>
+      </c>
+      <c r="F71" s="4">
+        <v>-123.2013765645745</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E72" s="7">
+        <v>49.13470108606343</v>
+      </c>
+      <c r="F72" s="7">
+        <v>-123.2019176903017</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="E73" s="7">
+        <v>49.13470108606343</v>
+      </c>
+      <c r="F73" s="7">
+        <v>-123.2019176903017</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="E74" s="7">
+        <v>49.136129174330662</v>
+      </c>
+      <c r="F74" s="7">
+        <v>-123.20221369782691</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="E75" s="7">
+        <v>49.136129174330662</v>
+      </c>
+      <c r="F75" s="7">
+        <v>-123.20221369782691</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E76" s="4">
+        <v>49.208616666666657</v>
+      </c>
+      <c r="F76" s="4">
+        <v>-123.20569999999999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E77" s="4">
+        <v>49.208616666666657</v>
+      </c>
+      <c r="F77" s="4">
+        <v>-123.20569999999999</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A78" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E78" s="4">
+        <v>49.208616666666657</v>
+      </c>
+      <c r="F78" s="4">
+        <v>-123.20569999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="E79" s="4">
+        <v>49.168816666666672</v>
+      </c>
+      <c r="F79" s="4">
+        <v>-123.2052333333333</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E80" s="4">
+        <v>49.168066666666661</v>
+      </c>
+      <c r="F80" s="4">
+        <v>-123.2047</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E81" s="7">
+        <v>49.130683333333323</v>
+      </c>
+      <c r="F81" s="7">
+        <v>-123.2143333333333</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="E82" s="7">
+        <v>49.130683333333323</v>
+      </c>
+      <c r="F82" s="7">
+        <v>-123.2143333333333</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A83" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="E83" s="4">
+        <v>49.130683333333323</v>
+      </c>
+      <c r="F83" s="4">
+        <v>-123.2143333333333</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A84" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="E84" s="4">
+        <v>49.130683333333323</v>
+      </c>
+      <c r="F84" s="4">
+        <v>-123.2143333333333</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A85" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="E85" s="4">
+        <v>49.130683333333323</v>
+      </c>
+      <c r="F85" s="4">
+        <v>-123.2143333333333</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A86" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E86" s="4">
+        <v>49.130683333333323</v>
+      </c>
+      <c r="F86" s="4">
+        <v>-123.2143333333333</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A87" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="E87" s="4">
+        <v>49.130683333333323</v>
+      </c>
+      <c r="F87" s="4">
+        <v>-123.2143333333333</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A88" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="E88" s="4">
+        <v>49.130683333333323</v>
+      </c>
+      <c r="F88" s="4">
+        <v>-123.2143333333333</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A89" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="E89" s="4">
+        <v>49.130683333333323</v>
+      </c>
+      <c r="F89" s="4">
+        <v>-123.2143333333333</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A90" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="E90" s="4">
+        <v>49.130683333333323</v>
+      </c>
+      <c r="F90" s="4">
+        <v>-123.2143333333333</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A91" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="E91" s="4">
+        <v>49.130683333333323</v>
+      </c>
+      <c r="F91" s="4">
+        <v>-123.2143333333333</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A92" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E92" s="4">
+        <v>49.130683333333323</v>
+      </c>
+      <c r="F92" s="4">
+        <v>-123.2143333333333</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A93" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E93" s="4">
+        <v>49.130683333333323</v>
+      </c>
+      <c r="F93" s="4">
+        <v>-123.2143333333333</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A94" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E94" s="4">
+        <v>49.130683333333323</v>
+      </c>
+      <c r="F94" s="4">
+        <v>-123.2143333333333</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A95" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E95" s="4">
+        <v>49.131083333333343</v>
+      </c>
+      <c r="F95" s="4">
+        <v>-123.21605</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A96" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="E96" s="4">
+        <v>49.131083333333343</v>
+      </c>
+      <c r="F96" s="4">
+        <v>-123.21605</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="E97" s="4">
+        <v>49.131083333333343</v>
+      </c>
+      <c r="F97" s="4">
+        <v>-123.21605</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="E98" s="10">
+        <v>49.120983333333328</v>
+      </c>
+      <c r="F98" s="10">
+        <v>-123.2120833333333</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="E99" s="10">
+        <v>49.120983333333328</v>
+      </c>
+      <c r="F99" s="10">
+        <v>-123.2120833333333</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="E100" s="4">
+        <v>49.120983333333328</v>
+      </c>
+      <c r="F100" s="4">
+        <v>-123.2120833333333</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D101" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="E101" s="10">
+        <v>49.11846666666667</v>
+      </c>
+      <c r="F101" s="10">
+        <v>-123.2077833333333</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D102" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="E102" s="10">
+        <v>49.11846666666667</v>
+      </c>
+      <c r="F102" s="10">
+        <v>-123.2077833333333</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C103" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E103" s="7">
+        <v>49.220966666666669</v>
+      </c>
+      <c r="F103" s="7">
+        <v>-123.21644999999999</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E104" s="7">
+        <v>49.220966666666669</v>
+      </c>
+      <c r="F104" s="7">
+        <v>-123.21644999999999</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E105" s="7">
+        <v>49.220966666666669</v>
+      </c>
+      <c r="F105" s="7">
+        <v>-123.21644999999999</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E106" s="7">
+        <v>49.220966666666669</v>
+      </c>
+      <c r="F106" s="7">
+        <v>-123.21644999999999</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E107" s="4">
+        <v>49.126724899047311</v>
+      </c>
+      <c r="F107" s="4">
+        <v>-123.20293871968271</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="E108" s="9">
+        <v>49.248722000000001</v>
+      </c>
+      <c r="F108" s="9">
+        <v>-121.950503</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="E109" s="4">
+        <v>49.142465999999999</v>
+      </c>
+      <c r="F109" s="4">
+        <v>-123.05259599999999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E110" s="7">
+        <v>49.127678505875281</v>
+      </c>
+      <c r="F110" s="7">
+        <v>-123.20287214948119</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="E111" s="7">
+        <v>49.127678505875281</v>
+      </c>
+      <c r="F111" s="7">
+        <v>-123.20287214948119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A112" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E112" s="7">
+        <v>49.127678505875281</v>
+      </c>
+      <c r="F112" s="7">
+        <v>-123.20287214948119</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A113" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E113" s="7">
+        <v>49.127678505875281</v>
+      </c>
+      <c r="F113" s="7">
+        <v>-123.20287214948119</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A114" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E114" s="7">
+        <v>49.127678505875281</v>
+      </c>
+      <c r="F114" s="7">
+        <v>-123.20287214948119</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A115" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="E115" s="7">
+        <v>49.127678505875281</v>
+      </c>
+      <c r="F115" s="7">
+        <v>-123.20287214948119</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A116" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E116" s="7">
+        <v>49.127678505875281</v>
+      </c>
+      <c r="F116" s="7">
+        <v>-123.20287214948119</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A117" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E117" s="7">
+        <v>49.127678505875281</v>
+      </c>
+      <c r="F117" s="7">
+        <v>-123.20287214948119</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A118" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E118" s="11">
+        <v>49.127400000000002</v>
+      </c>
+      <c r="F118" s="11">
+        <v>-123.201683</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A119" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B119" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="C119" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="E119" s="4">
+        <v>49.187058999999998</v>
+      </c>
+      <c r="F119" s="4">
+        <v>-123.141897</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A120" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B120" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C120" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D120" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="E120" s="4">
+        <v>49.187058999999998</v>
+      </c>
+      <c r="F120" s="4">
+        <v>-123.141897</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A121" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B121" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="C121" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D121" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E121" s="5">
+        <v>49.174500000000002</v>
+      </c>
+      <c r="F121" s="5">
+        <v>-123.16968300000001</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A122" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B122" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C122" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D122" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="E122" s="4">
+        <v>49.178899999999999</v>
+      </c>
+      <c r="F122" s="4">
+        <v>-123.18073333333329</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A123" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B123" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="E123" s="4">
+        <v>49.221400873139089</v>
+      </c>
+      <c r="F123" s="4">
+        <v>-123.20811005491331</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A124" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B124" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D124" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="E124" s="4">
+        <v>49.221400873139089</v>
+      </c>
+      <c r="F124" s="4">
+        <v>-123.20811005491331</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A125" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B125" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C125" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D125" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="E125" s="5">
+        <v>49.1113</v>
+      </c>
+      <c r="F125" s="5">
+        <v>-123.20021699999999</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A126" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B126" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="E126" s="5">
+        <v>49.111499999999999</v>
+      </c>
+      <c r="F126" s="5">
+        <v>-123.19881700000001</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A127" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B127" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C127" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D127" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="E127" s="5">
+        <v>49.111499999999999</v>
+      </c>
+      <c r="F127" s="5">
+        <v>-123.19881700000001</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A128" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B128" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="E128" s="5">
+        <v>49.111499999999999</v>
+      </c>
+      <c r="F128" s="5">
+        <v>-123.19881700000001</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="C129" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="E129" s="7">
+        <v>49.225999999999999</v>
+      </c>
+      <c r="F129" s="7">
+        <v>-123.2254333333333</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A130" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="C130" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="E130" s="7">
+        <v>49.225999999999999</v>
+      </c>
+      <c r="F130" s="7">
+        <v>-123.2254333333333</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A131" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B131" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="C131" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D131" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="E131" s="4">
+        <v>49.225999999999999</v>
+      </c>
+      <c r="F131" s="4">
+        <v>-123.2254333333333</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="E132" s="7">
+        <v>49.239833333333337</v>
+      </c>
+      <c r="F132" s="7">
+        <v>-123.2486833333333</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="E133" s="7">
+        <v>49.232116666666677</v>
+      </c>
+      <c r="F133" s="7">
+        <v>-123.2361666666667</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A134" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B134" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C134" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="E134" s="4">
+        <v>49.238466666666667</v>
+      </c>
+      <c r="F134" s="4">
+        <v>-123.24741666666669</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A135" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C135" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D135" s="4" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A136" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B136" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="C136" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D136" s="4" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A137" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C137" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D137" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="E137" s="4">
+        <v>49.107016666666667</v>
+      </c>
+      <c r="F137" s="4">
+        <v>-123.2007333333333</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A138" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B138" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C138" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D138" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="E138" s="4">
+        <v>49.107016666666667</v>
+      </c>
+      <c r="F138" s="4">
+        <v>-123.2007333333333</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A139" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B139" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="E139" s="5">
+        <v>49.107016999999999</v>
+      </c>
+      <c r="F139" s="5">
+        <v>-123.200733</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A140" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B140" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C140" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D140" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="E140" s="4">
+        <v>49.071989343585031</v>
+      </c>
+      <c r="F140" s="4">
+        <v>-123.1640264703845</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A141" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="C141" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D141" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="E141" s="7">
+        <v>49.071989343585031</v>
+      </c>
+      <c r="F141" s="7">
+        <v>-123.1640264703845</v>
+      </c>
+      <c r="G141" s="10" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A142" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B142" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C142" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D142" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="E142" s="4">
+        <v>49.071989343585031</v>
+      </c>
+      <c r="F142" s="4">
+        <v>-123.1640264703845</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A143" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B143" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C143" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D143" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="E143" s="4">
+        <v>49.066865165076841</v>
+      </c>
+      <c r="F143" s="4">
+        <v>-123.1622627727718</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A144" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B144" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="C144" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D144" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="E144" s="4">
+        <v>49.104116332388983</v>
+      </c>
+      <c r="F144" s="4">
+        <v>-123.1530238221343</v>
+      </c>
+      <c r="G144" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B145" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="C145" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D145" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="E145" s="4">
+        <v>49.104116332388983</v>
+      </c>
+      <c r="F145" s="4">
+        <v>-123.1530238221343</v>
+      </c>
+      <c r="G145" s="4" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D146" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="E146" s="7">
+        <v>49.104116332388983</v>
+      </c>
+      <c r="F146" s="7">
+        <v>-123.1530238221343</v>
+      </c>
+      <c r="G146" s="10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A147" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D147" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="E147" s="7">
+        <v>49.104116332388983</v>
+      </c>
+      <c r="F147" s="7">
+        <v>-123.1530238221343</v>
+      </c>
+      <c r="G147" s="10" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A148" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D148" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="E148" s="7">
+        <v>49.104116332388983</v>
+      </c>
+      <c r="F148" s="7">
+        <v>-123.1530238221343</v>
+      </c>
+      <c r="G148" s="10" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A149" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D149" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="E149" s="13">
+        <v>49.104117000000002</v>
+      </c>
+      <c r="F149" s="13">
+        <v>-123.15298300000001</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A150" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D150" s="10" t="s">
+        <v>397</v>
+      </c>
+      <c r="E150" s="13">
+        <v>49.104117000000002</v>
+      </c>
+      <c r="F150" s="13">
+        <v>-123.15298300000001</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A151" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D151" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="E151" s="13">
+        <v>49.104117000000002</v>
+      </c>
+      <c r="F151" s="13">
+        <v>-123.15298300000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A152" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="B152" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="E152" s="12">
+        <v>49.211199999999998</v>
+      </c>
+      <c r="F152" s="12">
+        <v>-123.20075</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A153" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B153" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C153" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D153" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="E153" s="4">
+        <v>49.213661000000002</v>
+      </c>
+      <c r="F153" s="4">
+        <v>-123.19337400000001</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A154" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B154" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C154" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D154" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="E154" s="4">
+        <v>49.213661000000002</v>
+      </c>
+      <c r="F154" s="4">
+        <v>-123.19337400000001</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A155" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B155" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C155" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D155" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E155" s="4">
+        <v>49.213091704061434</v>
+      </c>
+      <c r="F155" s="4">
+        <v>-123.1774527739064</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A156" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B156" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C156" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D156" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E156" s="4">
+        <v>49.213091704061434</v>
+      </c>
+      <c r="F156" s="4">
+        <v>-123.1774527739064</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A157" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B157" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C157" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D157" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E157" s="4">
+        <v>49.213091704061434</v>
+      </c>
+      <c r="F157" s="4">
+        <v>-123.1774527739064</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A158" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C158" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D158" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E158" s="4">
+        <v>49.213091704061434</v>
+      </c>
+      <c r="F158" s="4">
+        <v>-123.1774527739064</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A159" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="B159" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C159" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="E159" s="4">
+        <v>49.213661000000002</v>
+      </c>
+      <c r="F159" s="4">
+        <v>-123.19337400000001</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A160" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B160" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C160" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D160" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E160" s="4">
+        <v>49.189649999999993</v>
+      </c>
+      <c r="F160" s="4">
+        <v>-122.9625166666667</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A161" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B161" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="C161" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D161" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E161" s="4">
+        <v>49.12971666666666</v>
+      </c>
+      <c r="F161" s="4">
+        <v>-123.21316666666669</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C162" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D162" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E162" s="4">
+        <v>49.12971666666666</v>
+      </c>
+      <c r="F162" s="4">
+        <v>-123.21316666666669</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B163" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C163" s="4" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B164" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B165" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="E165" s="5">
+        <v>49.009633000000001</v>
+      </c>
+      <c r="F165" s="5">
+        <v>-123.104783</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B166" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="E166" s="4">
+        <v>49.232833333333339</v>
+      </c>
+      <c r="F166" s="4">
+        <v>-123.23765</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A167" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B167" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E167" s="4">
+        <v>49.232833333333339</v>
+      </c>
+      <c r="F167" s="4">
+        <v>-123.23765</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B168" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E168" s="4">
+        <v>49.231166666666667</v>
+      </c>
+      <c r="F168" s="4">
+        <v>-123.2348333333333</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B169" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="E169" s="4">
+        <v>49.231166666666667</v>
+      </c>
+      <c r="F169" s="4">
+        <v>-123.2348333333333</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B170" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E170" s="4">
+        <v>49.231166666666667</v>
+      </c>
+      <c r="F170" s="4">
+        <v>-123.2348333333333</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B171" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E171" s="4">
+        <v>49.231166666666667</v>
+      </c>
+      <c r="F171" s="4">
+        <v>-123.2348333333333</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B172" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C172" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="E172" s="5">
+        <v>49.042749999999998</v>
+      </c>
+      <c r="F172" s="5">
+        <v>-123.20398299999999</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B173" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E173" s="5">
+        <v>49.127400000000002</v>
+      </c>
+      <c r="F173" s="5">
+        <v>-123.201683</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E174" s="4">
+        <v>49.198938285918757</v>
+      </c>
+      <c r="F174" s="4">
+        <v>-123.1240583520557</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E175" s="4">
+        <v>49.198938285918757</v>
+      </c>
+      <c r="F175" s="4">
+        <v>-123.1240583520557</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A176" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="E176" s="4">
+        <v>49.104469000000002</v>
+      </c>
+      <c r="F176" s="4">
+        <v>-123.119963</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A177" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B177" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E177" s="4">
+        <v>49.208893197215183</v>
+      </c>
+      <c r="F177" s="4">
+        <v>-123.1588086801454</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B178" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E178" s="4">
+        <v>49.209249060993017</v>
+      </c>
+      <c r="F178" s="4">
+        <v>-123.1585449900756</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A179" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B179" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E179" s="4">
+        <v>49.209249060993017</v>
+      </c>
+      <c r="F179" s="4">
+        <v>-123.1585449900756</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A180" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E180" s="4">
+        <v>49.209249060993017</v>
+      </c>
+      <c r="F180" s="4">
+        <v>-123.1585449900756</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A181" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E181" s="7">
+        <v>49.209249060993017</v>
+      </c>
+      <c r="F181" s="7">
+        <v>-123.1585449900756</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A182" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E182" s="7">
+        <v>49.208607256591847</v>
+      </c>
+      <c r="F182" s="7">
+        <v>-123.1581208465588</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A183" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B183" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E183" s="4">
+        <v>49.208607256591847</v>
+      </c>
+      <c r="F183" s="4">
+        <v>-123.1581208465588</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A184" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B184" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="E184" s="4">
+        <v>49.161795087856483</v>
+      </c>
+      <c r="F184" s="4">
+        <v>-122.98210813238001</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A185" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B185" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E185" s="4">
+        <v>49.191299999999998</v>
+      </c>
+      <c r="F185" s="4">
+        <v>-122.92501666666671</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A186" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B186" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E186" s="4">
+        <v>49.191299999999998</v>
+      </c>
+      <c r="F186" s="4">
+        <v>-122.92501666666671</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A187" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="B187" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="E187" s="4">
+        <v>49.198799000000001</v>
+      </c>
+      <c r="F187" s="4">
+        <v>-122.925786</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A188" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B188" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="E188" s="4">
+        <v>49.199314531086728</v>
+      </c>
+      <c r="F188" s="4">
+        <v>-123.12242857374881</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A189" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B189" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E189" s="4">
+        <v>49.198357300482193</v>
+      </c>
+      <c r="F189" s="4">
+        <v>-123.1248498383337</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A190" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B190" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A191" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B191" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="E191" s="4">
+        <v>49.174325765605957</v>
+      </c>
+      <c r="F191" s="4">
+        <v>-123.16548795708</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A192" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B192" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="E192" s="4">
+        <v>49.174517423045799</v>
+      </c>
+      <c r="F192" s="4">
+        <v>-123.1676462533308</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A193" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B193" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E193" s="4">
+        <v>49.173905028496037</v>
+      </c>
+      <c r="F193" s="4">
+        <v>-123.16578163382729</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A194" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B194" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="E194" s="4">
+        <v>49.17414939361155</v>
+      </c>
+      <c r="F194" s="4">
+        <v>-123.16780951614069</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A195" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B195" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C195" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E195" s="4">
+        <v>49.104379000000002</v>
+      </c>
+      <c r="F195" s="4">
+        <v>-123.105102</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A196" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B196" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C196" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D196" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="E196" s="4">
+        <v>49.104379326042547</v>
+      </c>
+      <c r="F196" s="4">
+        <v>-123.1051018483179</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A197" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B197" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C197" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D197" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E197" s="4">
+        <v>49.098862410579649</v>
+      </c>
+      <c r="F197" s="4">
+        <v>-123.14209326902549</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A198" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B198" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="C198" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E198" s="4">
+        <v>49.207766666666657</v>
+      </c>
+      <c r="F198" s="4">
+        <v>-123.2607666666667</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A199" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C199" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E199" s="4">
+        <v>49.201483333333343</v>
+      </c>
+      <c r="F199" s="4">
+        <v>-123.2501166666667</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A200" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="C200" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E200" s="4">
+        <v>49.201483333333343</v>
+      </c>
+      <c r="F200" s="4">
+        <v>-123.2501166666667</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A201" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B201" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C201" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E201" s="4">
+        <v>49.168916666666668</v>
+      </c>
+      <c r="F201" s="4">
+        <v>-123.2499833333333</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A202" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B202" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C202" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E202" s="4">
+        <v>49.168916666666668</v>
+      </c>
+      <c r="F202" s="4">
+        <v>-123.2499833333333</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A203" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B203" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C203" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E203" s="4">
+        <v>49.168916666666668</v>
+      </c>
+      <c r="F203" s="4">
+        <v>-123.2499833333333</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A204" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B204" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C204" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E204" s="4">
+        <v>49.168916666666668</v>
+      </c>
+      <c r="F204" s="4">
+        <v>-123.2499833333333</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A205" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B205" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C205" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E205" s="4">
+        <v>49.149366666666658</v>
+      </c>
+      <c r="F205" s="4">
+        <v>-123.2373333333333</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A206" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B206" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="C206" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E206" s="4">
+        <v>49.149366666666658</v>
+      </c>
+      <c r="F206" s="4">
+        <v>-123.2373333333333</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A207" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="C207" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E207" s="4">
+        <v>49.149366666666658</v>
+      </c>
+      <c r="F207" s="4">
+        <v>-123.2373333333333</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A208" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B208" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="C208" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E208" s="4">
+        <v>49.094366666666659</v>
+      </c>
+      <c r="F208" s="4">
+        <v>-123.20921666666671</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A209" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D209" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="E209" s="5">
+        <v>49.042749999999998</v>
+      </c>
+      <c r="F209" s="5">
+        <v>-123.20398299999999</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A210" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B210" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="C210" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="D210" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="E210" s="5">
+        <v>49.042749999999998</v>
+      </c>
+      <c r="F210" s="5">
+        <v>-123.20398299999999</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A211" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="C211" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="E211" s="4">
+        <v>49.239533333333327</v>
+      </c>
+      <c r="F211" s="4">
+        <v>-123.2581666666667</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A212" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B212" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C212" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="D212" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="E212" s="7">
+        <v>49.191299999999998</v>
+      </c>
+      <c r="F212" s="7">
+        <v>-122.92501666666671</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A213" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B213" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C213" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D213" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E213" s="7">
+        <v>49.20187649740091</v>
+      </c>
+      <c r="F213" s="7">
+        <v>-123.12467681851879</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A214" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B214" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="C214" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D214" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="E214" s="4">
+        <v>49.159233</v>
+      </c>
+      <c r="F214" s="4">
+        <v>-122.99678299999999</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A215" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B215" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C215" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E215" s="4">
+        <v>49.159233333333333</v>
+      </c>
+      <c r="F215" s="4">
+        <v>-122.9967833333333</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A216" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B216" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C216" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="E216" s="4">
+        <v>49.128625219716277</v>
+      </c>
+      <c r="F216" s="4">
+        <v>-123.2084197998615</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A217" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B217" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C217" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="E217" s="4">
+        <v>49.213374000000002</v>
+      </c>
+      <c r="F217" s="4">
+        <v>-122.894358</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A218" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B218" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C218" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E218" s="4">
+        <v>49.181827381003743</v>
+      </c>
+      <c r="F218" s="4">
+        <v>-122.9734573279999</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A219" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B219" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C219" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D219" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E219" s="4">
+        <v>49.181632453785816</v>
+      </c>
+      <c r="F219" s="4">
+        <v>-122.97328249690921</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A220" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B220" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C220" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D220" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E220" s="4">
+        <v>49.176693386145303</v>
+      </c>
+      <c r="F220" s="4">
+        <v>-123.18594695423</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A221" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B221" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C221" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D221" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E221" s="4">
+        <v>49.178577144186342</v>
+      </c>
+      <c r="F221" s="4">
+        <v>-123.19150601916191</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A222" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B222" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C222" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D222" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E222" s="4">
+        <v>49.180605714746527</v>
+      </c>
+      <c r="F222" s="4">
+        <v>-123.1907300874055</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A223" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B223" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D223" s="4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A224" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B224" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C224" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D224" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E224" s="4">
+        <v>49.176710101034352</v>
+      </c>
+      <c r="F224" s="4">
+        <v>-123.1876076208609</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A225" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B225" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C225" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D225" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="E225" s="4">
+        <v>49.016797441686272</v>
+      </c>
+      <c r="F225" s="4">
+        <v>-123.113998430583</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A226" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B226" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D226" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E226" s="4">
+        <v>49.013268181336549</v>
+      </c>
+      <c r="F226" s="4">
+        <v>-123.1218256210031</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A227" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B227" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C227" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E227" s="4">
+        <v>49.138751999999997</v>
+      </c>
+      <c r="F227" s="4">
+        <v>-123.04091099999999</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A228" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B228" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C228" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D228" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E228" s="4">
+        <v>49.138752213980823</v>
+      </c>
+      <c r="F228" s="4">
+        <v>-123.04091113275391</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A229" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B229" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C229" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D229" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="E229" s="4">
+        <v>49.136054999999999</v>
+      </c>
+      <c r="F229" s="4">
+        <v>-123.03615600000001</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A230" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D230" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="E230" s="4">
+        <v>49.136054999999999</v>
+      </c>
+      <c r="F230" s="4">
+        <v>-123.03615600000001</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A231" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B231" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C231" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E231" s="4">
+        <v>49.147646000000002</v>
+      </c>
+      <c r="F231" s="4">
+        <v>-123.003196</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A232" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B232" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D232" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E232" s="4">
+        <v>49.147646078043302</v>
+      </c>
+      <c r="F232" s="4">
+        <v>-123.0031958238466</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A233" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B233" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C233" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E233" s="4">
+        <v>49.148539</v>
+      </c>
+      <c r="F233" s="4">
+        <v>-123.012269</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A234" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="B234" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C234" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D234" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="E234" s="4">
+        <v>49.181286</v>
+      </c>
+      <c r="F234" s="4">
+        <v>-122.967598</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A235" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B235" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="C235" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D235" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="E235" s="4">
+        <v>49.146884</v>
+      </c>
+      <c r="F235" s="4">
+        <v>-123.00229899999999</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A236" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B236" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="C236" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D236" s="4" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A237" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B237" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C237" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D237" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E237" s="4">
+        <v>49.205666666666673</v>
+      </c>
+      <c r="F237" s="4">
+        <v>-123.0627333333333</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A238" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B238" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D238" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="E238" s="4">
+        <v>49.201365000000003</v>
+      </c>
+      <c r="F238" s="4">
+        <v>-123.075011</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A239" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="B239" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="C239" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E239" s="4">
+        <v>49.131166999999998</v>
+      </c>
+      <c r="F239" s="4">
+        <v>-123.21885</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A240" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B240" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C240" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D240" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E240" s="4">
+        <v>49.210418530610653</v>
+      </c>
+      <c r="F240" s="4">
+        <v>-123.16029516333489</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A241" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B241" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C241" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D241" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E241" s="4">
+        <v>49.210418530610653</v>
+      </c>
+      <c r="F241" s="4">
+        <v>-123.16029516333489</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A242" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B242" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C242" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="D242" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E242" s="4">
+        <v>49.209939501522243</v>
+      </c>
+      <c r="F242" s="4">
+        <v>-123.15929609644699</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A243" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C243" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D243" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E243" s="4">
+        <v>49.209939501522243</v>
+      </c>
+      <c r="F243" s="4">
+        <v>-123.15929609644699</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A244" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B244" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C244" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D244" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E244" s="4">
+        <v>49.210669236998903</v>
+      </c>
+      <c r="F244" s="4">
+        <v>-123.1610914764677</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A245" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B245" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="C245" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E245" s="4">
+        <v>49.210107999999998</v>
+      </c>
+      <c r="F245" s="4">
+        <v>-123.160712</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A246" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B246" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C246" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="D246" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="E246" s="4">
+        <v>49.211107407245599</v>
+      </c>
+      <c r="F246" s="4">
+        <v>-123.1620966706251</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H285">
+    <sortCondition ref="A2:A285"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>